--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T16:18:25+00:00</t>
+    <t>2026-02-03T11:48:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T11:48:04+00:00</t>
+    <t>2026-02-24T11:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T11:13:53+00:00</t>
+    <t>2026-03-27T15:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T15:52:17+00:00</t>
+    <t>2026-05-05T11:38:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T11:38:42+00:00</t>
+    <t>2026-05-06T13:04:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T13:04:43+00:00</t>
+    <t>2026-05-12T13:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T13:23:02+00:00</t>
+    <t>2026-05-29T12:43:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T12:43:09+00:00</t>
+    <t>2026-05-29T14:49:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T14:49:05+00:00</t>
+    <t>2026-06-30T21:35:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T21:35:56+00:00</t>
+    <t>2026-05-29T14:49:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T14:49:05+00:00</t>
+    <t>2026-07-03T12:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T12:24:31+00:00</t>
+    <t>2026-07-07T21:14:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/www/terminologies/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T21:14:23+00:00</t>
+    <t>2026-07-29T14:36:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
